--- a/howell14.xlsx
+++ b/howell14.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Feb 19, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 07, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 22</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,267 +613,267 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 89</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t>Name 42</t>
+        </is>
+      </c>
+      <c r="D11" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Name 23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Name 51</t>
+        </is>
+      </c>
+      <c r="D12" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Name 52</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Name 27</t>
+        </is>
+      </c>
+      <c r="D13" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Name 37</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Name 76</t>
         </is>
       </c>
-      <c r="D11" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E11" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="D14" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 30</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Name 34</t>
         </is>
       </c>
-      <c r="D12" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E12" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="D15" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 65</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 83</t>
         </is>
       </c>
-      <c r="D13" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E13" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="D16" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 37</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Name 60</t>
+        </is>
+      </c>
+      <c r="D17" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Name 52</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Name 65</t>
+        </is>
+      </c>
+      <c r="D18" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Name 62</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Name 63</t>
+        </is>
+      </c>
+      <c r="D19" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Name 19</t>
         </is>
       </c>
-      <c r="D14" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E14" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 45</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D20" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 73</t>
         </is>
       </c>
-      <c r="D15" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E15" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Name 76</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Name 81</t>
-        </is>
-      </c>
-      <c r="D16" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E16" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Name 32</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Name 61</t>
-        </is>
-      </c>
-      <c r="D17" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E17" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Name 69</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Name 83</t>
-        </is>
-      </c>
-      <c r="D18" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E18" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Name 66</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D21" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Name 68</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Name 65</t>
         </is>
       </c>
-      <c r="D19" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E19" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Name 89</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Name 54</t>
-        </is>
-      </c>
-      <c r="D20" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E20" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Name 71</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Name 12</t>
-        </is>
-      </c>
-      <c r="D21" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E21" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Name 87</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Name 53</t>
-        </is>
-      </c>
       <c r="D22" s="4">
         <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$P$3:$P$184)/26</f>
         <v/>
@@ -889,12 +889,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D23" s="4">

--- a/howell14.xlsx
+++ b/howell14.xlsx
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 89</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,150 +636,150 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 23</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
+        <is>
+          <t>Name 76</t>
+        </is>
+      </c>
+      <c r="D12" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Name 85</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Name 79</t>
+        </is>
+      </c>
+      <c r="D13" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Name 62</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Name 61</t>
+        </is>
+      </c>
+      <c r="D14" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Name 54</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Name 24</t>
+        </is>
+      </c>
+      <c r="D15" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Name 13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Name 44</t>
+        </is>
+      </c>
+      <c r="D16" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Name 63</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Name 70</t>
+        </is>
+      </c>
+      <c r="D17" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Name 51</t>
         </is>
       </c>
-      <c r="D12" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E12" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Name 52</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Name 27</t>
-        </is>
-      </c>
-      <c r="D13" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E13" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Name 37</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Name 76</t>
-        </is>
-      </c>
-      <c r="D14" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E14" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Name 30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Name 34</t>
-        </is>
-      </c>
-      <c r="D15" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E15" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Name 65</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Name 83</t>
-        </is>
-      </c>
-      <c r="D16" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E16" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Name 37</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Name 60</t>
-        </is>
-      </c>
-      <c r="D17" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E17" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Name 52</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -797,12 +797,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 62</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Name 19</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="D20" s="4">
@@ -843,12 +843,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="D21" s="4">
@@ -866,12 +866,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Name 68</t>
+          <t>Name 23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D22" s="4">
@@ -889,12 +889,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="D23" s="4">

--- a/howell14.xlsx
+++ b/howell14.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 07, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 08, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 62</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 52</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 62</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 76</t>
+          <t>Name 19</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 75</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 79</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 62</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 13</t>
+          <t>Name 90</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 41</t>
         </is>
       </c>
       <c r="D16" s="4">
@@ -751,7 +751,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 56</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -802,7 +802,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -825,7 +825,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="D20" s="4">
@@ -843,12 +843,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="D21" s="4">
@@ -866,12 +866,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Name 23</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 51</t>
         </is>
       </c>
       <c r="D22" s="4">
@@ -889,12 +889,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="D23" s="4">

--- a/howell14.xlsx
+++ b/howell14.xlsx
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 62</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 52</t>
+          <t>Name 87</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 74</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 62</t>
+          <t>Name 40</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,60 +636,60 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 12</t>
+          <t>Name 35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
+        <is>
+          <t>Name 71</t>
+        </is>
+      </c>
+      <c r="D12" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Name 87</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Name 86</t>
+        </is>
+      </c>
+      <c r="D13" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Name 51</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Name 19</t>
         </is>
       </c>
-      <c r="D12" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E12" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Name 75</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Name 34</t>
-        </is>
-      </c>
-      <c r="D13" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E13" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Name 50</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Name 22</t>
-        </is>
-      </c>
       <c r="D14" s="4">
         <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
         <v/>
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 90</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 41</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="D16" s="4">
@@ -751,12 +751,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -774,12 +774,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 81</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -797,12 +797,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 89</t>
         </is>
       </c>
       <c r="D20" s="4">
@@ -843,12 +843,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 79</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="D21" s="4">
@@ -866,12 +866,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 23</t>
         </is>
       </c>
       <c r="D22" s="4">
@@ -889,12 +889,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="D23" s="4">

--- a/howell14.xlsx
+++ b/howell14.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 08, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 10, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 87</t>
+          <t>Name 36</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 74</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 40</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 35</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 87</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,104 +682,104 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Name 27</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Name 13</t>
+        </is>
+      </c>
+      <c r="D14" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Name 65</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Name 81</t>
+        </is>
+      </c>
+      <c r="D15" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Name 51</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Name 53</t>
+        </is>
+      </c>
+      <c r="D16" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Name 19</t>
         </is>
       </c>
-      <c r="D14" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E14" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
-          <t>Name 17</t>
+          <t>Name 83</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D17" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Name 67</t>
         </is>
       </c>
-      <c r="D15" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E15" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Name 26</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Name 43</t>
-        </is>
-      </c>
-      <c r="D16" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E16" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Name 27</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Name 55</t>
-        </is>
-      </c>
-      <c r="D17" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E17" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Name 15</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 81</t>
+          <t>Name 89</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -797,12 +797,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 77</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name 89</t>
+          <t>Name 56</t>
         </is>
       </c>
       <c r="D20" s="4">
@@ -843,12 +843,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Name 79</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="D21" s="4">
@@ -866,12 +866,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Name 23</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="D22" s="4">
@@ -889,12 +889,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 76</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Name 17</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="D23" s="4">

--- a/howell14.xlsx
+++ b/howell14.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 10, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 11, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,311 +590,311 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
+        <is>
+          <t>Name 57</t>
+        </is>
+      </c>
+      <c r="D10" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=1",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=1",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=1",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=1",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Name 27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Name 66</t>
+        </is>
+      </c>
+      <c r="D11" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Name 36</t>
         </is>
       </c>
-      <c r="D10" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=1",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=1",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E10" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=1",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=1",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Name 34</t>
+        </is>
+      </c>
+      <c r="D12" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Name 26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Name 83</t>
+        </is>
+      </c>
+      <c r="D13" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Name 39</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Name 56</t>
+        </is>
+      </c>
+      <c r="D14" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Name 78</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 86</t>
         </is>
       </c>
-      <c r="D11" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E11" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="D15" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 24</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 35</t>
         </is>
       </c>
-      <c r="D12" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E12" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="D16" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 37</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 89</t>
         </is>
       </c>
-      <c r="D13" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E13" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="D17" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 36</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
-          <t>Name 13</t>
+          <t>Name 58</t>
         </is>
       </c>
-      <c r="D14" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E14" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="D18" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 23</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Name 80</t>
+        </is>
+      </c>
+      <c r="D19" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Name 69</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Name 81</t>
         </is>
       </c>
-      <c r="D15" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E15" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="D20" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 74</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Name 77</t>
+        </is>
+      </c>
+      <c r="D21" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Name 67</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Name 34</t>
+        </is>
+      </c>
+      <c r="D22" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E22" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Name 53</t>
         </is>
       </c>
-      <c r="D16" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E16" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Name 19</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Name 83</t>
-        </is>
-      </c>
-      <c r="D17" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E17" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Name 67</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Name 89</t>
-        </is>
-      </c>
-      <c r="D18" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E18" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Name 47</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Name 77</t>
-        </is>
-      </c>
-      <c r="D19" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E19" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Name 67</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Name 56</t>
-        </is>
-      </c>
-      <c r="D20" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E20" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Name 83</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Name 66</t>
-        </is>
-      </c>
-      <c r="D21" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E21" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Name 22</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Name 32</t>
-        </is>
-      </c>
-      <c r="D22" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E22" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Name 76</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Name 65</t>
         </is>
       </c>
       <c r="D23" s="4">

--- a/howell14.xlsx
+++ b/howell14.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 11, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 18, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,267 +590,267 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
+        <is>
+          <t>Name 87</t>
+        </is>
+      </c>
+      <c r="D10" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=1",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=1",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=1",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=1",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Name 19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Name 81</t>
+        </is>
+      </c>
+      <c r="D11" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Name 63</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Name 12</t>
+        </is>
+      </c>
+      <c r="D12" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Name 85</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Name 60</t>
+        </is>
+      </c>
+      <c r="D13" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Name 57</t>
         </is>
       </c>
-      <c r="D10" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=1",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=1",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E10" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=1",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=1",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 74</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D14" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 90</t>
         </is>
       </c>
-      <c r="D11" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E11" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=2",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=2",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
-          <t>Name 36</t>
+          <t>Name 45</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Name 34</t>
-        </is>
-      </c>
-      <c r="D12" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E12" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=3",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=3",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Name 26</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="D15" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Name 83</t>
         </is>
       </c>
-      <c r="D13" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E13" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=4",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=4",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 32</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D16" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 13</t>
         </is>
       </c>
-      <c r="D14" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E14" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 46</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D17" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 75</t>
         </is>
       </c>
-      <c r="D15" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E15" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 43</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D18" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Name 84</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Name 54</t>
+        </is>
+      </c>
+      <c r="D19" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Name 54</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Name 43</t>
+        </is>
+      </c>
+      <c r="D20" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Name 45</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Name 35</t>
         </is>
       </c>
-      <c r="D16" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E16" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Name 37</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Name 89</t>
-        </is>
-      </c>
-      <c r="D17" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E17" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Name 36</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Name 58</t>
-        </is>
-      </c>
-      <c r="D18" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E18" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Name 23</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Name 80</t>
-        </is>
-      </c>
-      <c r="D19" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E19" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Name 69</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Name 81</t>
-        </is>
-      </c>
-      <c r="D20" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E20" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Name 74</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Name 77</t>
-        </is>
-      </c>
       <c r="D21" s="4">
         <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$P$3:$P$184)/26</f>
         <v/>
@@ -866,12 +866,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 90</t>
         </is>
       </c>
       <c r="D22" s="4">
@@ -889,12 +889,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 68</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="D23" s="4">

--- a/howell14.xlsx
+++ b/howell14.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 18, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 20, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 87</t>
+          <t>Name 72</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 19</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 81</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 12</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,219 +682,219 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 57</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
+        <is>
+          <t>Name 53</t>
+        </is>
+      </c>
+      <c r="D14" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Name 36</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Name 69</t>
+        </is>
+      </c>
+      <c r="D15" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Name 86</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Name 31</t>
+        </is>
+      </c>
+      <c r="D16" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Name 69</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Name 11</t>
+        </is>
+      </c>
+      <c r="D17" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Name 50</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Name 32</t>
+        </is>
+      </c>
+      <c r="D18" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Name 32</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Name 46</t>
+        </is>
+      </c>
+      <c r="D19" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Name 67</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Name 47</t>
+        </is>
+      </c>
+      <c r="D20" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Name 11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Name 72</t>
+        </is>
+      </c>
+      <c r="D21" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Name 36</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Name 46</t>
+        </is>
+      </c>
+      <c r="D22" s="4">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$P$3:$P$184)/26</f>
+        <v/>
+      </c>
+      <c r="E22" s="5">
+        <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$N$3:$N$184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Name 74</t>
         </is>
       </c>
-      <c r="D14" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E14" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=5",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=5",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Name 90</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Name 45</t>
-        </is>
-      </c>
-      <c r="D15" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E15" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=6",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=6",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Name 83</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Name 32</t>
-        </is>
-      </c>
-      <c r="D16" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E16" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=7",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=7",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Name 13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Name 46</t>
-        </is>
-      </c>
-      <c r="D17" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E17" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=8",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=8",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Name 75</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Name 43</t>
-        </is>
-      </c>
-      <c r="D18" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E18" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=9",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=9",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Name 84</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Name 54</t>
-        </is>
-      </c>
-      <c r="D19" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E19" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=10",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=10",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Name 54</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Name 43</t>
-        </is>
-      </c>
-      <c r="D20" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E20" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=11",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=11",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Name 45</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Name 35</t>
-        </is>
-      </c>
-      <c r="D21" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E21" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=12",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=12",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Name 11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Name 90</t>
-        </is>
-      </c>
-      <c r="D22" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$O$3:$O$184)/26+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$P$3:$P$184)/26</f>
-        <v/>
-      </c>
-      <c r="E22" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$184,"=13",'By Board'!$M$3:$M$184)+SUMIF('By Board'!$E$3:$E$184,"=13",'By Board'!$N$3:$N$184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Name 68</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 24</t>
         </is>
       </c>
       <c r="D23" s="4">
